--- a/outputs/excel/energy_rates.xlsx
+++ b/outputs/excel/energy_rates.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,47 +428,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Plan Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Rate ($/kWh)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Term (Months)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Renewable %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cancel Fee</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Signup Link</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Learn More Link</t>
         </is>

--- a/outputs/excel/energy_rates.xlsx
+++ b/outputs/excel/energy_rates.xlsx
@@ -425,10 +425,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -489,22 +489,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Live Brighter SS 8</t>
+          <t>Easy Choice 3 - Residential</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Direct Energy Services, LLC</t>
+          <t>ENH Power</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$0.10190</t>
+          <t>$0.09790</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -519,12 +519,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>888-836-6141</t>
+          <t>1-833-488-3147</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.providerpower.com/nh/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -536,22 +536,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Live Brighter AE 7</t>
+          <t>Think Basic 6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Direct Energy Services, LLC</t>
+          <t>Think Energy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$0.10190</t>
+          <t>$0.09800</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -566,12 +566,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>888-836-6141</t>
+          <t>1-833-669-3080</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.thinkenergy.com/?utm_source=rateboard&amp;utm_medium=referral&amp;utm_campaign=newhampshire" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -583,22 +583,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Live Brighter TO 9</t>
+          <t>Power Your Tomorrow Fixed - 6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Direct Energy Services, LLC</t>
+          <t>Town Square Energy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>$0.10490</t>
+          <t>$0.10070</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>888-836-6141</t>
+          <t>1-877-430-0093</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.townsquareenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -630,17 +630,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Think Basic 7</t>
+          <t>Live Brighter AE 7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Think Energy</t>
+          <t>Direct Energy Services, LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$0.10800</t>
+          <t>$0.10390</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -660,12 +660,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1-833-669-3080</t>
+          <t>888-836-6141</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.thinkenergy.com/?utm_source=rateboard&amp;utm_medium=referral&amp;utm_campaign=newhampshire" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Live Brighter 6</t>
+          <t>Live Brighter SS 7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>$0.10890</t>
+          <t>$0.10490</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -724,22 +724,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Go Green Lights 8</t>
+          <t>Embrace Green 6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Direct Energy Services, LLC</t>
+          <t>CleanSky Energy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>$0.11190</t>
+          <t>$0.10990</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -749,17 +749,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>$50.00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>888-836-6141</t>
+          <t>1-888-355-6205</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://cleanskyenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Live Brighter 11</t>
+          <t>Live Brighter 6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>$0.11590</t>
+          <t>$0.10990</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -818,22 +818,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Live Brighter AE 13</t>
+          <t>Power Your Tomorrow Variable - 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Direct Energy Services, LLC</t>
+          <t>Town Square Energy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>$0.11990</t>
+          <t>$0.11260</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>888-836-6141</t>
+          <t>1-877-430-0093</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.townsquareenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -865,42 +865,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Simple Power 12 - Residential</t>
+          <t>Go Green Lights 8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENH Power</t>
+          <t>Direct Energy Services, LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>$0.12490</t>
+          <t>$0.11390</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>$100.00</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1-833-488-3147</t>
+          <t>888-836-6141</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.providerpower.com/nh/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -912,27 +912,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SmartEnergy -  Web Only Rate</t>
+          <t>Live Brighter TO 9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SmartEnergy</t>
+          <t>Direct Energy Services, LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>$0.12600</t>
+          <t>$0.11390</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1-800-760-1207</t>
+          <t>888-836-6141</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;a href="http://account.smartenergy.com/new-hampshire?utm_source=PUC_Site_NH&amp;utm_medium=referral&amp;utm_campaign=exclusive_online_rate" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -959,17 +959,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SureLock 12 - Residential</t>
+          <t>White Mountain Select 12 Month Term</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>XOOM Energy New Hampshire, LLC</t>
+          <t>Ambit Energy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>$0.12790</t>
+          <t>$0.12000</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -984,17 +984,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>$110.00</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1-888-997-8979</t>
+          <t>1-877-282-6248</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://ww2.ambitenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1006,42 +1006,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SimpleClean12 - Residential</t>
+          <t>Power Your Tomorrow Variable - 1 Green</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>XOOM Energy New Hampshire, LLC</t>
+          <t>Town Square Energy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>$0.12990</t>
+          <t>$0.12000</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>$110.00</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1-888-997-8979</t>
+          <t>1-877-430-0093</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.townsquareenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1053,42 +1053,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8 Month Standard Fixed</t>
+          <t>Embrace Green 24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>North American Power &amp; Gas, LLC</t>
+          <t>CleanSky Energy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>$0.12990</t>
+          <t>$0.12490</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>$10.00</t>
+          <t>$150.00</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>877-572-9965</t>
+          <t>1-888-355-6205</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.napower.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://cleanskyenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Embrace Green 24</t>
+          <t>Embrace Green 12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>$0.12990</t>
+          <t>$0.12490</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>$150.00</t>
+          <t>$75.00</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1147,42 +1147,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ultra Clean Solar 24</t>
+          <t>Ultimate Perks 12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CleanSky Energy</t>
+          <t>Ambit Energy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>$0.13090</t>
+          <t>$0.12500</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>$150.00</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1-888-355-6205</t>
+          <t>1-877-282-6248</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;a href="http://cleanskyenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://ww2.ambitenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1194,42 +1194,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SureLock 24</t>
+          <t>Affordable Wind 12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>XOOM Energy New Hampshire, LLC</t>
+          <t>CleanSky Energy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>$0.13190</t>
+          <t>$0.12590</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>$200.00</t>
+          <t>$75.00</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1-888-997-8979</t>
+          <t>1-888-355-6205</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://cleanskyenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1241,42 +1241,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10 Month Standard Fixed</t>
+          <t>Ultra Clean Solar 24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>North American Power &amp; Gas, LLC</t>
+          <t>CleanSky Energy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>$0.13290</t>
+          <t>$0.12590</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>$10.00</t>
+          <t>$150.00</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>877-572-9965</t>
+          <t>1-888-355-6205</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.napower.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://cleanskyenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1288,17 +1288,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RescueLock 12</t>
+          <t>SmartEnergy -  Web Only Rate</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>XOOM Energy New Hampshire, LLC</t>
+          <t>SmartEnergy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>$0.13390</t>
+          <t>$0.12600</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1308,22 +1308,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>$110.00</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1-888-997-8979</t>
+          <t>1-800-760-1207</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://account.smartenergy.com/new-hampshire?utm_source=PUC_Site_NH&amp;utm_medium=referral&amp;utm_campaign=exclusive_online_rate" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1335,17 +1335,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Embrace Green 6</t>
+          <t>6 Month Standard Fixed</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CleanSky Energy</t>
+          <t>North American Power &amp; Gas, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>$0.13490</t>
+          <t>$0.12690</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1355,22 +1355,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>$50.00</t>
+          <t>$10.00</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1-888-355-6205</t>
+          <t>877-572-9965</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;a href="http://cleanskyenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.napower.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1382,42 +1382,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Embrace Green 12</t>
+          <t>Live Brighter AE 13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CleanSky Energy</t>
+          <t>Direct Energy Services, LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>$0.13490</t>
+          <t>$0.12790</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>$75.00</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1-888-355-6205</t>
+          <t>888-836-6141</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;a href="http://cleanskyenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1429,42 +1429,42 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Affordable Wind 12</t>
+          <t>Power Your Tomorrow Fixed - 4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CleanSky Energy</t>
+          <t>Town Square Energy</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>$0.13590</t>
+          <t>$0.13050</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>$75.00</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1-888-355-6205</t>
+          <t>1-877-430-0093</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;a href="http://cleanskyenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.townsquareenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1476,42 +1476,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Think Clean 12</t>
+          <t>14 Month Standard Fixed</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Think Energy</t>
+          <t>North American Power &amp; Gas, LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>$0.13900</t>
+          <t>$0.13290</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>$10.00</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1-833-669-3080</t>
+          <t>877-572-9965</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.thinkenergy.com/?utm_source=rateboard&amp;utm_medium=referral&amp;utm_campaign=newhampshire" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.napower.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1523,22 +1523,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>White Mountain Select 12 Month Term</t>
+          <t>Live Brighter 11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ambit Energy</t>
+          <t>Direct Energy Services, LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>$0.14000</t>
+          <t>$0.13290</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1553,12 +1553,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1-877-282-6248</t>
+          <t>888-836-6141</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;a href="http://ww2.ambitenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1570,17 +1570,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ultimate Perks 12</t>
+          <t>SureLock 12 - Residential</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ambit Energy</t>
+          <t>XOOM Energy New Hampshire, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>$0.14500</t>
+          <t>$0.13390</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>$110.00</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1-877-282-6248</t>
+          <t>1-888-997-8979</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;a href="http://ww2.ambitenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1617,42 +1617,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Think Clean 36</t>
+          <t>Simple Power 12 - Residential</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Think Energy</t>
+          <t>ENH Power</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>$0.14600</t>
+          <t>$0.13490</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>$100.00</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1-833-669-3080</t>
+          <t>1-833-488-3147</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.thinkenergy.com/?utm_source=rateboard&amp;utm_medium=referral&amp;utm_campaign=newhampshire" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.providerpower.com/nh/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SimpleClean</t>
+          <t>SureLock 24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1674,22 +1674,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>$0.16490</t>
+          <t>$0.13690</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>$200.00</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1711,17 +1711,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Winter Break 12</t>
+          <t>SimpleClean12 - Residential</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ambit Energy</t>
+          <t>XOOM Energy New Hampshire, LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>$0.18290</t>
+          <t>$0.13690</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1731,22 +1731,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>$110.00</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1-877-282-6248</t>
+          <t>1-888-997-8979</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>&lt;a href="http://ww2.ambitenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1758,45 +1758,327 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>RescueLock 12</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>XOOM Energy New Hampshire, LLC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>$0.14090</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>$110.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1-888-997-8979</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://www.energy.nh.gov/consumers/choosing-energy-supplier/choosing-energy-supplier-frequently-asked-questions" target="_blank"&gt;Learn more&lt;/a&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Think Clean 12</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Think Energy</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>$0.14800</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1-833-669-3080</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>&lt;a href="http://www.thinkenergy.com/?utm_source=rateboard&amp;utm_medium=referral&amp;utm_campaign=newhampshire" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://www.energy.nh.gov/consumers/choosing-energy-supplier/choosing-energy-supplier-frequently-asked-questions" target="_blank"&gt;Learn more&lt;/a&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Think Clean 24</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Think Energy</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>$0.14900</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1-833-669-3080</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>&lt;a href="http://www.thinkenergy.com/?utm_source=rateboard&amp;utm_medium=referral&amp;utm_campaign=newhampshire" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://www.energy.nh.gov/consumers/choosing-energy-supplier/choosing-energy-supplier-frequently-asked-questions" target="_blank"&gt;Learn more&lt;/a&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Power Your Tomorrow Fixed - 4 Green</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Town Square Energy</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>$0.15000</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1-877-430-0093</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>&lt;a href="http://www.townsquareenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://www.energy.nh.gov/consumers/choosing-energy-supplier/choosing-energy-supplier-frequently-asked-questions" target="_blank"&gt;Learn more&lt;/a&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Winter Break 12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ambit Energy</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>$0.16000</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1-877-282-6248</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>&lt;a href="http://ww2.ambitenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://www.energy.nh.gov/consumers/choosing-energy-supplier/choosing-energy-supplier-frequently-asked-questions" target="_blank"&gt;Learn more&lt;/a&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SimpleClean</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>XOOM Energy New Hampshire, LLC</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>$0.16490</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1-888-997-8979</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://www.energy.nh.gov/consumers/choosing-energy-supplier/choosing-energy-supplier-frequently-asked-questions" target="_blank"&gt;Learn more&lt;/a&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Winter Break 24</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Ambit Energy</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>$0.18590</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>$0.16500</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>1-877-282-6248</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>&lt;a href="http://ww2.ambitenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>&lt;a href="https://www.energy.nh.gov/consumers/choosing-energy-supplier/choosing-energy-supplier-frequently-asked-questions" target="_blank"&gt;Learn more&lt;/a&gt;</t>
         </is>

--- a/outputs/excel/energy_rates.xlsx
+++ b/outputs/excel/energy_rates.xlsx
@@ -425,10 +425,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -489,22 +489,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Easy Choice 3 - Residential</t>
+          <t>Power Your Tomorrow Fixed - 6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ENH Power</t>
+          <t>Town Square Energy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$0.09790</t>
+          <t>$0.10070</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -519,12 +519,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1-833-488-3147</t>
+          <t>1-877-430-0093</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.providerpower.com/nh/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.townsquareenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -536,17 +536,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Think Basic 6</t>
+          <t>SmartEnergy -  Web Only Rate</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Think Energy</t>
+          <t>SmartEnergy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$0.09800</t>
+          <t>$0.10900</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -566,12 +566,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1-833-669-3080</t>
+          <t>1-800-760-1207</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.thinkenergy.com/?utm_source=rateboard&amp;utm_medium=referral&amp;utm_campaign=newhampshire" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://account.smartenergy.com/new-hampshire?utm_source=PUC_Site_NH&amp;utm_medium=referral&amp;utm_campaign=exclusive_online_rate" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -583,17 +583,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Power Your Tomorrow Fixed - 6</t>
+          <t>Embrace Green 6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Town Square Energy</t>
+          <t>CleanSky Energy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>$0.10070</t>
+          <t>$0.10990</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -603,22 +603,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>$50.00</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1-877-430-0093</t>
+          <t>1-888-355-6205</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.townsquareenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://cleanskyenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Live Brighter AE 7</t>
+          <t>Live Brighter SS 6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$0.10390</t>
+          <t>$0.11090</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -677,22 +677,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Live Brighter SS 7</t>
+          <t>Power Your Today Variable - 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Direct Energy Services, LLC</t>
+          <t>Town Square Energy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>$0.10490</t>
+          <t>$0.11260</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>888-836-6141</t>
+          <t>1-877-430-0093</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.townsquareenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -724,42 +724,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Embrace Green 6</t>
+          <t>Easy Choice 3 - Residential</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CleanSky Energy</t>
+          <t>ENH Power</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>$0.10990</t>
+          <t>$0.11290</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>$50.00</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1-888-355-6205</t>
+          <t>1-833-488-3147</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;a href="http://cleanskyenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.providerpower.com/nh/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -771,27 +771,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Live Brighter 6</t>
+          <t>Power Your Today Variable - 1 Green</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Direct Energy Services, LLC</t>
+          <t>Town Square Energy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>$0.10990</t>
+          <t>$0.12260</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>888-836-6141</t>
+          <t>1-877-430-0093</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.townsquareenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -818,22 +818,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Power Your Tomorrow Variable - 1</t>
+          <t>Live Brighter AE 7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Town Square Energy</t>
+          <t>Direct Energy Services, LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>$0.11260</t>
+          <t>$0.12290</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1-877-430-0093</t>
+          <t>888-836-6141</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.townsquareenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -865,27 +865,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Go Green Lights 8</t>
+          <t>White Mountain Select 12 Month Term</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Direct Energy Services, LLC</t>
+          <t>Ambit Energy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>$0.11390</t>
+          <t>$0.13090</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>888-836-6141</t>
+          <t>1-877-282-6248</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://ww2.ambitenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -912,22 +912,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Live Brighter TO 9</t>
+          <t>Power Your Today Fixed - 6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Direct Energy Services, LLC</t>
+          <t>Town Square Energy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>$0.11390</t>
+          <t>$0.13140</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>888-836-6141</t>
+          <t>1-877-430-0093</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.townsquareenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -959,22 +959,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>White Mountain Select 12 Month Term</t>
+          <t>16 Month Standard Fixed</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ambit Energy</t>
+          <t>North American Power &amp; Gas, LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>$0.12000</t>
+          <t>$0.13290</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -984,17 +984,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>$10.00</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1-877-282-6248</t>
+          <t>877-572-9965</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;a href="http://ww2.ambitenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.napower.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1006,22 +1006,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Power Your Tomorrow Variable - 1 Green</t>
+          <t>Embrace Green 24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Town Square Energy</t>
+          <t>CleanSky Energy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>$0.12000</t>
+          <t>$0.13290</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>$150.00</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1-877-430-0093</t>
+          <t>1-888-355-6205</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.townsquareenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://cleanskyenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1053,42 +1053,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Embrace Green 24</t>
+          <t>Live Brighter AE 13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CleanSky Energy</t>
+          <t>Direct Energy Services, LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>$0.12490</t>
+          <t>$0.13490</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>$150.00</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1-888-355-6205</t>
+          <t>888-836-6141</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;a href="http://cleanskyenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>$0.12490</t>
+          <t>$0.13490</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>$0.12500</t>
+          <t>$0.13590</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1194,42 +1194,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Affordable Wind 12</t>
+          <t>14 Month Standard Fixed</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CleanSky Energy</t>
+          <t>North American Power &amp; Gas, LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>$0.12590</t>
+          <t>$0.13590</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>$75.00</t>
+          <t>$10.00</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1-888-355-6205</t>
+          <t>877-572-9965</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;a href="http://cleanskyenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.napower.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1241,22 +1241,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ultra Clean Solar 24</t>
+          <t>Simply Clean 12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CleanSky Energy</t>
+          <t>CleanChoice Energy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>$0.12590</t>
+          <t>$0.13600</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>$150.00</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1-888-355-6205</t>
+          <t>1-800-460-4900</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;a href="http://cleanskyenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://mycleanchoice.com/nhshoppera12" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1288,27 +1288,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SmartEnergy -  Web Only Rate</t>
+          <t>Live Brighter 11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SmartEnergy</t>
+          <t>Direct Energy Services, LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>$0.12600</t>
+          <t>$0.14290</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1-800-760-1207</t>
+          <t>888-836-6141</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;a href="http://account.smartenergy.com/new-hampshire?utm_source=PUC_Site_NH&amp;utm_medium=referral&amp;utm_campaign=exclusive_online_rate" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1335,22 +1335,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6 Month Standard Fixed</t>
+          <t>Live Brighter 23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>North American Power &amp; Gas, LLC</t>
+          <t>Direct Energy Services, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>$0.12690</t>
+          <t>$0.14290</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>$10.00</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>877-572-9965</t>
+          <t>888-836-6141</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.napower.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1382,22 +1382,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Live Brighter AE 13</t>
+          <t>Simple Power 12 - Residential</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Direct Energy Services, LLC</t>
+          <t>ENH Power</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>$0.12790</t>
+          <t>$0.14290</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1407,17 +1407,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>$100.00</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>888-836-6141</t>
+          <t>1-833-488-3147</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.providerpower.com/nh/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1429,22 +1429,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Power Your Tomorrow Fixed - 4</t>
+          <t>SureLock 12 - Residential</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Town Square Energy</t>
+          <t>XOOM Energy New Hampshire, LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>$0.13050</t>
+          <t>$0.14490</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1454,17 +1454,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>$110.00</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1-877-430-0093</t>
+          <t>1-888-997-8979</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.townsquareenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1476,22 +1476,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>14 Month Standard Fixed</t>
+          <t>SureLock 24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>North American Power &amp; Gas, LLC</t>
+          <t>XOOM Energy New Hampshire, LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>$0.13290</t>
+          <t>$0.14590</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>$10.00</t>
+          <t>$200.00</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>877-572-9965</t>
+          <t>1-888-997-8979</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.napower.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1523,42 +1523,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Live Brighter 11</t>
+          <t>SimpleClean12 - Residential</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Direct Energy Services, LLC</t>
+          <t>XOOM Energy New Hampshire, LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>$0.13290</t>
+          <t>$0.14690</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>$110.00</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>888-836-6141</t>
+          <t>1-888-997-8979</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1570,22 +1570,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SureLock 12 - Residential</t>
+          <t>Live Brighter TO 9</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>XOOM Energy New Hampshire, LLC</t>
+          <t>Direct Energy Services, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>$0.13390</t>
+          <t>$0.14690</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>$110.00</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1-888-997-8979</t>
+          <t>888-836-6141</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1617,42 +1617,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Simple Power 12 - Residential</t>
+          <t>Go Green Lights 8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ENH Power</t>
+          <t>Direct Energy Services, LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>$0.13490</t>
+          <t>$0.14790</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>$100.00</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1-833-488-3147</t>
+          <t>888-836-6141</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.providerpower.com/nh/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1664,42 +1664,42 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SureLock 24</t>
+          <t>Think Clean 12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>XOOM Energy New Hampshire, LLC</t>
+          <t>Think Energy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>$0.13690</t>
+          <t>$0.14800</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>$200.00</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1-888-997-8979</t>
+          <t>1-833-669-3080</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.thinkenergy.com/?utm_source=rateboard&amp;utm_medium=referral&amp;utm_campaign=newhampshire" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1711,42 +1711,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SimpleClean12 - Residential</t>
+          <t>Think Clean 24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>XOOM Energy New Hampshire, LLC</t>
+          <t>Think Energy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>$0.13690</t>
+          <t>$0.14900</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>$110.00</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1-888-997-8979</t>
+          <t>1-833-669-3080</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.thinkenergy.com/?utm_source=rateboard&amp;utm_medium=referral&amp;utm_campaign=newhampshire" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>$0.14090</t>
+          <t>$0.15190</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1805,22 +1805,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Think Clean 12</t>
+          <t>Power Your Today Fixed - 6 Green</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Think Energy</t>
+          <t>Town Square Energy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>$0.14800</t>
+          <t>$0.15880</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1-833-669-3080</t>
+          <t>1-877-430-0093</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.thinkenergy.com/?utm_source=rateboard&amp;utm_medium=referral&amp;utm_campaign=newhampshire" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.townsquareenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1852,27 +1852,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Think Clean 24</t>
+          <t>SimpleClean</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Think Energy</t>
+          <t>XOOM Energy New Hampshire, LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>$0.14900</t>
+          <t>$0.16490</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1-833-669-3080</t>
+          <t>1-888-997-8979</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.thinkenergy.com/?utm_source=rateboard&amp;utm_medium=referral&amp;utm_campaign=newhampshire" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1899,27 +1899,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Power Your Tomorrow Fixed - 4 Green</t>
+          <t>Winter Break 12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Town Square Energy</t>
+          <t>Ambit Energy</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>$0.15000</t>
+          <t>$0.17290</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1929,12 +1929,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1-877-430-0093</t>
+          <t>1-877-282-6248</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.townsquareenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://ww2.ambitenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Winter Break 12</t>
+          <t>Winter Break 24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>$0.16000</t>
+          <t>$0.17790</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1985,100 +1985,6 @@
         </is>
       </c>
       <c r="I33" t="inlineStr">
-        <is>
-          <t>&lt;a href="https://www.energy.nh.gov/consumers/choosing-energy-supplier/choosing-energy-supplier-frequently-asked-questions" target="_blank"&gt;Learn more&lt;/a&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>SimpleClean</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>XOOM Energy New Hampshire, LLC</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>$0.16490</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>1-888-997-8979</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>&lt;a href="https://www.energy.nh.gov/consumers/choosing-energy-supplier/choosing-energy-supplier-frequently-asked-questions" target="_blank"&gt;Learn more&lt;/a&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Winter Break 24</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Ambit Energy</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>$0.16500</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>1-877-282-6248</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>&lt;a href="http://ww2.ambitenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
         <is>
           <t>&lt;a href="https://www.energy.nh.gov/consumers/choosing-energy-supplier/choosing-energy-supplier-frequently-asked-questions" target="_blank"&gt;Learn more&lt;/a&gt;</t>
         </is>
